--- a/test/generator/baseline/gen.html.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.html.to.xlsx.xlsx
@@ -325,8 +325,10 @@
       <c r="C3">
         <v>103</v>
       </c>
-      <c r="D3">
-        <v>7</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+7</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -364,8 +366,10 @@
       <c r="C6">
         <v>20</v>
       </c>
-      <c r="D6">
-        <v>4</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+4</t>
+        </is>
       </c>
     </row>
     <row r="7">

--- a/test/generator/baseline/gen.html.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.html.to.xlsx.xlsx
@@ -1018,196 +1018,203 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t xml:space="preserve">165 Inspirational Quotes To Keep You Motivated In Life</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t xml:space="preserve">There is no analogous technology in ebooks , so the conversion will usually end up placing the image either centered or floating close to the point in the text where it was inserted , not necessarily where it appears on the page in Word.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Lists</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t xml:space="preserve">All types of lists are supported by the conversion, with the exception of lists that use fancy bullets, these get converted to regular bullets.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Bulleted List</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">• One</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Two</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Numbered List</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">1. One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Two</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Multi-level List s</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">1. One</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three</t>
+          <t xml:space="preserve">1. Two</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
+          <t xml:space="preserve">1. Three</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">2. Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Six</t>
+          <t xml:space="preserve">3. Five</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Multi-level list with bullets:</t>
+          <t xml:space="preserve">2. Six</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">A Multi-level list with bullets:</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">• One</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bullet uses an image as the bullet item</t>
+          <t xml:space="preserve">• Two</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">• This bullet uses an image as the bullet item</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">• Four</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Five</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Continued Lists</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">1. One</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">An interruption in our regularly scheduled listing, for this essential and very relevant public service announcement.</t>
+          <t xml:space="preserve">2. Two</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">We now resume our normal programming</t>
+          <t xml:space="preserve">An interruption in our regularly scheduled listing, for this essential and very relevant public service announcement.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">3. We now resume our normal programming</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Four</t>
         </is>
       </c>
     </row>

--- a/test/generator/baseline/gen.html.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.html.to.xlsx.xlsx
@@ -1219,5 +1219,8 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A34" r:id="rId1"/>
+  </hyperlinks>
 </worksheet>
 </file>